--- a/daily_matches/job_matches_2026-10-09.xlsx
+++ b/daily_matches/job_matches_2026-10-09.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G57"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,17 +456,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Slalom Flex (Project Based)- ML Ops Engineer</t>
+          <t>B1 - AI Platform Engineer - Agentic AI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Slalom Consulting</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Albany, NY, USA USA</t>
+          <t>Charlotte, NC, USA USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -474,7 +474,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, scikit-learn, Data Lake, MLflow, FastAPI</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Gemini, BigQuery, MLflow, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -484,59 +484,59 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55e0624b44a35626</t>
+          <t>https://www.indeed.com/viewjob?jk=a26f6d29c9750839</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Atlanta, GA, USA USA</t>
+          <t>Alpharetta, GA, USA USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>22.2</v>
+        <v>21.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Gemini, Prompt Engineering, scikit-learn, Redshift, BigQuery, Dataflow</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Mistral, Prompt Engineering, Cortex, TensorFlow, PyTorch</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=803b407aed33b34c</t>
+          <t>https://www.indeed.com/viewjob?jk=aae768820263255e</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI ML Engineer-5</t>
+          <t>B2/C1 - AI Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Malvern, PA, USA USA</t>
+          <t>Charlotte, NC, USA USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -544,24 +544,24 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, AWS SageMaker, S3, MLflow, FastAPI, Docker</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, Gemini, BigQuery, MLflow, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e705edb0f9259ef</t>
+          <t>https://www.indeed.com/viewjob?jk=9e428958ad9e8a14</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Solution Enterprise Architect - Database L2</t>
+          <t>B2/C1 - AI Platform Engineer 2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -575,7 +575,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20</v>
+        <v>18.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -584,29 +584,29 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f492bdeb3fbf7cc</t>
+          <t>https://www.indeed.com/viewjob?jk=71e937de86f8de63</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>Full Stack Engineer, Back-end/Edge Development</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Westlake, TX, USA USA</t>
+          <t>Palo Alto, CA, USA USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -614,392 +614,392 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, S3, EC2, Kinesis, Docker, Kubernetes, CI/CD, Terraform</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, OpenCV, BigQuery, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c90944751a08861f</t>
+          <t>https://www.indeed.com/viewjob?jk=dfbf5011e801e14a</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Generative AI Engineer</t>
+          <t>Application Developer, Automation &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>J2B GLOBAL LLC</t>
+          <t>Cary Street Partners Financial</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, USA USA</t>
+          <t>Richmond, VA, USA USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.8</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Mistral, Pinecone, Prompt Engineering, FastAPI</t>
+          <t>AI Engineer, Copilot, FastAPI, Docker, Kubernetes, CI/CD, GitHub Actions, Git, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9320e817584de0d2</t>
+          <t>https://www.indeed.com/viewjob?jk=21151df2a228c0a3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NuAxis Innovations</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Research Triangle Park, NC, USA USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.8</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, Pinecone, TensorFlow, PyTorch, scikit-learn, MLflow, Apache Airflow, Snowflake</t>
+          <t>LangChain, RAG, Copilot, Prompt Engineering, Git, Snowflake, Kafka, MongoDB, NoSQL, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a11006b13bb999b</t>
+          <t>https://www.indeed.com/viewjob?jk=703acd54a03be894</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Scientist - Agentic AI</t>
+          <t>Cyber Security Engineer-Application Security Tooling (SCA/SAST/ DAST/ MAST/ API Security)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise | HPE</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>San Juan, PR, USA USA</t>
+          <t>Phoenix, AZ, USA USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.8</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Jenkins</t>
+          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Jenkins, Kafka, PostgreSQL, NoSQL, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8dbae72b28a5fe86</t>
+          <t>https://www.indeed.com/viewjob?jk=a9ed5a614020b926</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>FTS Network Services – Data Analytics Advisor</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Reston, VA, USA USA</t>
+          <t>Irving, TX, USA USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, MLflow, CI/CD, Git, Databricks</t>
+          <t>RAG, Data Lake, Git, Snowflake, Databricks, Kafka, Tableau, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96a354be84c2774c</t>
+          <t>https://www.indeed.com/viewjob?jk=39867fe787e05360</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Senior Data Engineer (F/H) - Niort</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Intuit</t>
+          <t>SFEIR</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Mountain View, CA, USA USA</t>
+          <t>DE, USA USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, TensorFlow, Keras, NLTK, AWS SageMaker, Docker, Kubernetes, CI/CD, Git</t>
+          <t>AI Engineer, RAG, BigQuery, Docker, Kubernetes, Snowflake, Databricks, BigQuery, Kafka, Python</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba2cfdc750e170ad</t>
+          <t>https://www.indeed.com/viewjob?jk=7ba4b6c64ac8f142</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Audience &amp; Marketing Insights Analyst</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ahead</t>
+          <t>Stanford University</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>USA USA</t>
+          <t>Stanford, CA, USA USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, Copilot, Prompt Engineering, CI/CD, Terraform, Git, NoSQL</t>
+          <t>BigQuery, CI/CD, GitHub Actions, Git, BigQuery, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee16caa44fa7461b</t>
+          <t>https://www.indeed.com/viewjob?jk=6907a6e1657f5124</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Digital Eng, Robotics &amp; Automation, Process Sciences, Analytics and Technology, CGT</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Competera</t>
+          <t>AstraZeneca</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Mateo, CA, USA USA</t>
+          <t>Los Angeles, CA, USA USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, TensorFlow, PyTorch, scikit-learn, LightGBM, CatBoost, Keras, Databricks, PySpark, Python</t>
+          <t>RAG, Data Lake, CI/CD, Git, NoSQL, Python, SQL, R, Java, C++</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23fd1f9b080e659e</t>
+          <t>https://www.indeed.com/viewjob?jk=2416671de542b0b4</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data &amp; Analytics Developer II - Data Scientist</t>
+          <t>Full-Stack Engineer 4 (Python, React, AWS)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Wet Coast Logistics</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Greenville, SC, USA USA</t>
+          <t>Cambridge, MA, USA USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Prompt Engineering, TensorFlow, PyTorch, scikit-learn, XGBoost, MLflow, Databricks, Power BI</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4930ffb452c6e901</t>
+          <t>https://www.indeed.com/viewjob?jk=62a73708df2af64b</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Gen AI Engineer-5</t>
+          <t>Full-stack Engineer 4 (Python/AWS)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Newark, DE, USA USA</t>
+          <t>Cambridge, MA, USA USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, FAISS, Pinecone, ChromaDB</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=219cdd5f8ec54ae9</t>
+          <t>https://www.indeed.com/viewjob?jk=a3f16cbf818d2cc7</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Quality Engineer - E2E Testing</t>
+          <t>ETL Engineer - Hybrid (Atlanta, GA)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>OneDigital</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA USA</t>
+          <t>Atlanta, GA, USA USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python</t>
+          <t>RAG, Copilot, Pinecone, Cortex, AKS, CI/CD, Git, Snowflake, Python, SQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f74b13b92fba8065</t>
+          <t>https://www.indeed.com/viewjob?jk=7f025291341db017</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AI/ML DevOps Engineer</t>
+          <t>Sr. Software Engineer, Infrastructure, Manufacturing Quality</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Austin, TX, USA USA</t>
+          <t>Fremont, CA, USA USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL</t>
+          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, Python, SQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1009,452 +1009,452 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5fcf0f91468d631</t>
+          <t>https://www.indeed.com/viewjob?jk=da5c97dfaad93985</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Development Test Engineer (SDET), AI &amp; Automation</t>
+          <t>Full-Stack Engineer 4 (Python, AWS) (Cloud Operations Resilience Engineering)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Keeper Security, Inc.</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>McLean, VA, USA USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0ef94bda4b1957d</t>
+          <t>https://www.indeed.com/viewjob?jk=1b650dac7a81d057</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI Applied Health System Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Rush University Medical Center</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Foster City, CA, USA USA</t>
+          <t>Chicago, IL, USA USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, TensorFlow, PyTorch, scikit-learn, Docker, Kubernetes, CI/CD, Python, R</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, CI/CD, Python, R, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9da0f3b564fc2123</t>
+          <t>https://www.indeed.com/viewjob?jk=0946c8ef475d429d</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Cyber - AI Cloud Security Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, USA USA</t>
+          <t>Las Vegas, NV, USA USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python</t>
+          <t>AI Engineer, Generative AI, RAG, Gemini, FastAPI, Kubernetes, Terraform, Python, R, Java</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a1830ef2a37b276</t>
+          <t>https://www.indeed.com/viewjob?jk=11444585e972490b</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Engineer- Machine Learning</t>
+          <t>Cyber -AI Cloud Security Engineer - Consultant</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Badger Meter</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, USA USA</t>
+          <t>Austin, TX, USA USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, EC2, Glue, Redshift, Git, Redshift, NoSQL, Python</t>
+          <t>AI Engineer, Generative AI, RAG, Gemini, FastAPI, Kubernetes, Terraform, Python, R, Java</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f970ca59d10265e</t>
+          <t>https://www.indeed.com/viewjob?jk=7220668203faf4aa</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Cyber - AI Cloud Security Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Pacific Life</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Newport Beach, CA, USA USA</t>
+          <t>San Antonio, TX, USA USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, Copilot, Cortex, CI/CD, Git, Snowflake, Python, SQL, R</t>
+          <t>AI Engineer, Generative AI, RAG, Gemini, FastAPI, Kubernetes, Terraform, Python, R, Java</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=145ea1e85469e08e</t>
+          <t>https://www.indeed.com/viewjob?jk=2898119af725f02e</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Personalization Product Senior Data Associate</t>
+          <t>Cyber -AI Cloud Security Engineer - Consultant</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New York, NY, USA USA</t>
+          <t>Morristown, NJ, USA USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, Data Lake, Git, Snowflake, Tableau, Python, SQL, R</t>
+          <t>AI Engineer, Generative AI, RAG, Gemini, FastAPI, Kubernetes, Terraform, Python, R, Java</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=220e7590b1937290</t>
+          <t>https://www.indeed.com/viewjob?jk=70386b814fbbb616</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Associate IT Officer, Data and Information Management (Associate Data Engineer)</t>
+          <t>Software Engineer, Backend, Level 4</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>World Bank Group</t>
+          <t>Snap Inc.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Washington, DC, USA USA</t>
+          <t>Los Angeles, CA, USA USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, CI/CD, Git, Databricks, PySpark, Power BI, Python, SQL</t>
+          <t>RAG, Kubernetes, Git, NoSQL, Python, SQL, R, Java, C++, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0aa6dd1b04fbce5</t>
+          <t>https://www.indeed.com/viewjob?jk=40d41a1bc586e7f3</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - FDE</t>
+          <t>Software Engineer - Data Platform (R37)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>R1 RCM</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Irving, TX, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Gemini, BigQuery, Terraform, Git, BigQuery, Python, R</t>
+          <t>Docker, Kubernetes, Terraform, Databricks, Kafka, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1cf48b0163f027a</t>
+          <t>https://www.indeed.com/viewjob?jk=a0637db8f75f44d4</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Machine Learning Engineer 2, Business Platform</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Intuit</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, USA USA</t>
+          <t>Mountain View, CA, USA USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, scikit-learn, Dataflow, CI/CD, Git, Snowflake, Power BI, Python</t>
+          <t>Data Scientist, Machine Learning Engineer, TensorFlow, Keras, NLTK, Git, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ed526d6ed5b191e</t>
+          <t>https://www.indeed.com/viewjob?jk=506b441047049e92</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Full Stack developer-5</t>
+          <t>Data Scientist Co-op</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Cox Automotive</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA USA</t>
+          <t>Atlanta, GA, USA USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, S3, Docker, Kubernetes, CI/CD, Git, NoSQL, SQL, R</t>
+          <t>Data Scientist, Generative AI, scikit-learn, Git, Snowflake, Tableau, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65f6cb7a15d84c49</t>
+          <t>https://www.indeed.com/viewjob?jk=29e745afba95a97c</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr. Azure Data Engineer with Databricks</t>
+          <t>Cyber - AI Cloud Security Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, USA USA</t>
+          <t>Portland, OR, USA USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Data Lake, CI/CD, Git, Databricks, PySpark, Power BI, Python, SQL</t>
+          <t>AI Engineer, Generative AI, RAG, Gemini, FastAPI, Kubernetes, Terraform, Python, R, Java</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a650bae5ce2865af</t>
+          <t>https://www.indeed.com/viewjob?jk=1d0b97e2a373425a</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Full Stack Engineer II</t>
+          <t>Cyber -AI Cloud Security Engineer - Consultant</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Medpro systems</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Mount Arlington, NJ, USA USA</t>
+          <t>Wichita, KS, USA USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RAG, Copilot, FastAPI, CI/CD, Git, Kafka, PostgreSQL, MongoDB, SQL, R</t>
+          <t>AI Engineer, Generative AI, RAG, Gemini, FastAPI, Kubernetes, Terraform, Python, R, Java</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4711747a7e234c3</t>
+          <t>https://www.indeed.com/viewjob?jk=60552ffb9123cec8</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Behavioral Biometrics</t>
+          <t>Agentic Software Engineer I</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Blackboard</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Morristown, NJ, USA USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, PyTorch, scikit-learn, XGBoost, LightGBM, AKS, Git, Python, R</t>
+          <t>Data Scientist, Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1464,32 +1464,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e34f022e3ea3569</t>
+          <t>https://www.indeed.com/viewjob?jk=000420415063525a</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AI Data Platform Engineer</t>
+          <t>Databricks Platform Architecture</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>AT&amp;T</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Alpharetta, GA, USA USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Snowflake, Databricks, BigQuery, Redshift, Kafka, R, Scala</t>
+          <t>Generative AI, RAG, Data Lake, CI/CD, Databricks, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1499,67 +1499,67 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e322091c12151da</t>
+          <t>https://www.indeed.com/viewjob?jk=08f9d16e37781b6e</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Platform &amp; Cloud Engineer, AI- Enabled Developer</t>
+          <t>Resident Engineer, AI Security</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Liberty company insurance brokers</t>
+          <t>A10 Networks</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Woodland Hills, CA, USA USA</t>
+          <t>Orlando, FL, USA USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, Terraform, Git, Tableau, Python, SQL, R, Java</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, PostgreSQL, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cea5cc81a279b30</t>
+          <t>https://www.indeed.com/viewjob?jk=1760bee835503efb</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Engineer, Data Services</t>
+          <t>AI-Native Software Engineering Americas Market</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>TrueML</t>
+          <t>Logic, Inc.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Chicago, IL, USA USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Glue, Athena, Kinesis, Terraform, Git, Kafka, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1569,54 +1569,54 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51dae1964caf1fbb</t>
+          <t>https://www.indeed.com/viewjob?jk=7a9aabd372cf1ed4</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Norstella</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Brentwood, TN, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Generative AI, Prompt Engineering, CI/CD, Snowflake, Databricks, Python, SQL, R, Java, Scala</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, scikit-learn, Git, Python, R</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52c9a93606e8b426</t>
+          <t>https://www.indeed.com/viewjob?jk=48418790045abc9a</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Data Science Advisor - Remote</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1625,151 +1625,151 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Snowflake, Databricks, BigQuery, Redshift, Kafka, R, Scala</t>
+          <t>RAG, TensorFlow, PyTorch, scikit-learn, Tableau, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f563024b3edfa1e7</t>
+          <t>https://www.indeed.com/viewjob?jk=eaeb2a87ed13cada</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Enterprise ServiceNow Architect</t>
+          <t>Senior Analyst – Financial Services Direct Mail Marketing Analytics</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Dentsu</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>MD, USA USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Snowflake, Databricks, BigQuery, Redshift, Kafka, R, Scala</t>
+          <t>BigQuery, BigQuery, Tableau, Python, SQL, R, Scala, Optimization, A/B Testing</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76d8be6b3de911a3</t>
+          <t>https://www.indeed.com/viewjob?jk=dfccbb2d0fd51968</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer--Embedded Systems</t>
+          <t>Data Engineer, Technology Risk</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Advanced Flow Solutions</t>
+          <t>Intercontinental Exchange</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, USA USA</t>
+          <t>Atlanta, GA, USA USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Docker, Jenkins, Git, Python, SQL, R, Java, C++</t>
+          <t>RAG, CI/CD, Git, Tableau, Power BI, Python, SQL, R, C++</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae31e1439788747c</t>
+          <t>https://www.indeed.com/viewjob?jk=3f1951c5ed9c6f5e</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr. Engineer, AI Cyber Security</t>
+          <t>BSP (Kernel / QNX) Software Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Capgemini Engineering</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Seattle, WA, USA USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Hugging Face, TensorFlow, PyTorch, AWS SageMaker, Databricks, Python, R</t>
+          <t>Generative AI, RAG, Gemini, CI/CD, Git, Python, R, C++, Scala</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d1567b1c8e5cc62</t>
+          <t>https://www.indeed.com/viewjob?jk=8a1c19289c2f844e</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer II - Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Uber</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>San Francisco, CA, USA USA</t>
+          <t>Boston, MA, USA USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, Kafka, Cassandra, Python, R, Java, C++, Scala, Optimization</t>
+          <t>Kubernetes, CI/CD, Terraform, Kafka, NoSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1779,637 +1779,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06cbe08baf6e39ad</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Senior Java Developer</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Intellibee Inc</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Boston, MA, USA USA</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Data Scientist, LangChain, CI/CD, NoSQL, Python, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4d72c08349cccd97</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Databricks Platform Architecture</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>AT&amp;T</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Plano, TX, USA USA</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Data Lake, CI/CD, Databricks, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a9c4f041e340ace9</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Sr. AI Engineer</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>SiTime Corporation</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Santa Clara, CA, USA USA</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>10</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, RAG, Copilot, CI/CD, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c583066481650fbd</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Handshake</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, USA USA</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>10</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, scikit-learn, Python, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c3e3f04065b70e9e</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Handshake</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, USA USA</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>10</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, scikit-learn, Python, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d7491a225eef9941</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Capgemini Invent, Consultant, AI Engineer</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Capgemini Invent</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, USA USA</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>10</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, RAG, Gemini, Git, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2f044b8c02ce80ad</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, AI Platform Integration</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Keeper Security, Inc.</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Remote, USA USA</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>10</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Copilot, Prompt Engineering, CI/CD, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e03b15f6f17d0203</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Senior Applied AI &amp; Agent Engineer</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>CSC</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Gaithersburg, MD, USA USA</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>10</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>RAG, S3, FastAPI, Docker, CI/CD, PostgreSQL, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4f94df6a51d0b9f3</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Software Engineer – Full Stack &amp; AI-Enabled Development</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Clayco</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>St. Louis, MO, USA USA</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>10</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, GitHub Actions, Git, PostgreSQL, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=395914343f733cf2</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer Graduate (E-Commerce User Growth) - 2027 Start (PhD)</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>TikTok</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Seattle, WA, USA USA</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>10</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Python, SQL, R, C++, Optimization</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b5f35e5a25369f99</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer - E-Commerce Recommendation Live</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>TikTok</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Seattle, WA, USA USA</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>10</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Python, R, C++, Optimization, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d60d921306465829</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>GenAI Engineer expert (Raritan, NJ .Hybrid)</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>COMPEST SOLUTIONS INDIA PRIVATE LIMITED</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Raritan, NJ, USA USA</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>10</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, RAG, CI/CD, Python, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2926d0734efbca47</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer (Seattle)</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Airwallex</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Seattle, WA, USA USA</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>10</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>BigQuery, Snowflake, BigQuery, PostgreSQL, MySQL, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c0ef35c3d0ab2f06</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Senior AI Analyst, People Digital Solutions</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Okta</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Bellevue, WA, USA USA</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>10</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Generative AI, Prompt Engineering, Git, Tableau, Power BI, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d8edd8f94fc9d958</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Senior Analyst – Financial Services Direct Mail Marketing Analytics</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Merkle, Inc.</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>USA USA</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>10</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>BigQuery, BigQuery, Tableau, Python, SQL, R, Scala, Optimization, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e1a6ff8a98a78ee4</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>AI Creative Technologist (176518)</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Colgate-Palmolive</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Overland Park, KS, USA USA</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>10</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0892c89d25f476e0</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Senior Software Developer</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Lenexa, KS, USA USA</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>10</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, S3, CI/CD, Git, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2903f876ff9765d7</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>IoT Engineer</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Cognizant</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Houston, TX, USA USA</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>10</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Git, MySQL, Python, SQL, R, Java, C++</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=012f4078e04e9452</t>
+          <t>https://www.indeed.com/viewjob?jk=3b69cb4c0ab9836b</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-10-09.xlsx
+++ b/daily_matches/job_matches_2026-10-09.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,25 +456,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - AI &amp; Cloud Platforms</t>
+          <t>Sr Software Engineer I - Enterprise Architecture</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>New York, NY, USA USA</t>
+          <t>Phoenix, AZ, USA USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.2</v>
+        <v>24.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Gemini, Prompt Engineering, BigQuery, FastAPI, Docker, Kubernetes</t>
+          <t>Generative AI, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -484,32 +484,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5673baac86fbad3</t>
+          <t>https://www.indeed.com/viewjob?jk=caff522a25e0d7d6</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Engineer</t>
+          <t>Gen AI Developer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Howmet Aerospace</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, USA USA</t>
+          <t>Dallas, TX, USA USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Hugging Face, TensorFlow, PyTorch, scikit-learn, spaCy, NLTK, Docker, Kubernetes, Apache Airflow, PySpark</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Hugging Face, Pinecone, TensorFlow, PyTorch, AWS SageMaker, Azure ML</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -519,24 +519,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34ebb49cffa42b9e</t>
+          <t>https://www.indeed.com/viewjob?jk=966968d140bf48e2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Enterprise Data Engineering - Software Engineer II - P2</t>
+          <t>Gen AI Developer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Credit One Bank</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, USA USA</t>
+          <t>Richardson, TX, USA USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -544,7 +544,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, EC2, Redshift, Kubernetes, Apache Airflow, CI/CD, Git, Redshift, Kafka, NoSQL</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Hugging Face, Pinecone, TensorFlow, PyTorch, AWS SageMaker, Azure ML</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -554,32 +554,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2de03d7d6acc99ef</t>
+          <t>https://www.indeed.com/viewjob?jk=84431b9d5a1a9068</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Financial Services - Forward Deployed Engineer - Technology Consulting - Senior - NYC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Boise, ID, USA USA</t>
+          <t>New York, NY, USA USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.8</v>
+        <v>18.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, GitHub Actions, Git</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Copilot, Pinecone, Prompt Engineering, AWS SageMaker, Azure ML, Docker</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -589,32 +589,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2896efcf20f6d63a</t>
+          <t>https://www.indeed.com/viewjob?jk=83aa91fe9a6b8f53</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Gen AI Developer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Shinebask Technologies</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, USA USA</t>
+          <t>Plano, TX, USA USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>18.9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, Hugging Face, TensorFlow, PyTorch, Azure ML, Docker, CI/CD</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Hugging Face, Pinecone, TensorFlow, PyTorch, AWS SageMaker, Azure ML</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -624,32 +624,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7a784545f4a7e52</t>
+          <t>https://www.indeed.com/viewjob?jk=3b98a756d58e2e27</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr. Python Data Engineer</t>
+          <t>AI Machine Learning Engineering Sr -</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Globant</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>GA, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>17.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, CI/CD, Terraform, Databricks, Dask, Python, SQL, R</t>
+          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, Docker, Kubernetes, Apache Airflow, CI/CD, Git, Kafka</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -659,24 +659,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9491761135bfafe3</t>
+          <t>https://www.indeed.com/viewjob?jk=25e732a62993b114</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SRE/DevOps Engineer</t>
+          <t>Azure Cloud Engineer II</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Magnet Forensics</t>
+          <t>Cleveland Clinic</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>USA USA</t>
+          <t>Cleveland, OH, USA USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -684,7 +684,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, EC2, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, Python, SQL</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -694,24 +694,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=278357c0443f7d7f</t>
+          <t>https://www.indeed.com/viewjob?jk=7c6069a1656fe1c8</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Scientist, Applied AI Solutions</t>
+          <t>Full Stack AI Developer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DLA Piper</t>
+          <t>Enterprise Knowledge</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Reston, VA, USA USA</t>
+          <t>Arlington, VA, USA USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -719,7 +719,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, scikit-learn, NLTK, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Docker, Git, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -729,32 +729,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff83dec193f92c33</t>
+          <t>https://www.indeed.com/viewjob?jk=ef4c8960caa195a5</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AI Engineer - REMOTE USA</t>
+          <t>Software Engineer II (Java/Full stack/Cloud)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Acliviti Consulting Group, LLC</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA USA</t>
+          <t>Westerville, OH, USA USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Prompt Engineering, CI/CD, Git, Python, R, Java, Scala, Optimization</t>
+          <t>Generative AI, RAG, Copilot, Prompt Engineering, S3, CI/CD, Git, SQL, R, Java</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -764,32 +764,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4be78f4e958360cd</t>
+          <t>https://www.indeed.com/viewjob?jk=af75619025565e2d</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Cyber -AI Cloud Security Engineer - Consultant</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, USA USA</t>
+          <t>Charlotte, NC, USA USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Gemini, FastAPI, Kubernetes, Terraform, Python, R, Java</t>
+          <t>Generative AI, RAG, Copilot, Prompt Engineering, S3, Docker, Kubernetes, Git, R, Java</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -799,32 +799,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd6d9fac6e0ce4b2</t>
+          <t>https://www.indeed.com/viewjob?jk=1db0b10090073bdc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Vibe Coding Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Meeru AI Inc</t>
+          <t>Hierarch Soft Technologies Inc,</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, XGBoost, LightGBM, GCP Vertex AI, Snowflake, PostgreSQL, Python, SQL, R</t>
+          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, Docker, Kubernetes, Git, Python, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -834,24 +834,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fce1ff51739afd1</t>
+          <t>https://www.indeed.com/viewjob?jk=5745a1b5dcde8af4</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Engineer, FW &amp; Product Test Eng</t>
+          <t>Cyber -AI Cloud Security Engineer - Consultant</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Longmont, CO, USA USA</t>
+          <t>McLean, VA, USA USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -859,7 +859,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Copilot, TensorFlow, PyTorch, scikit-learn, CI/CD, Git, Python, R, Scala</t>
+          <t>AI Engineer, Generative AI, RAG, Gemini, FastAPI, Kubernetes, Terraform, Python, R, Java</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -869,24 +869,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f84d0e3c26bf9ce2</t>
+          <t>https://www.indeed.com/viewjob?jk=c2a1f4e5b6141aed</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Cyber - AI Cloud Security Engineer - Senior Consultant</t>
+          <t>Associate Marketing Data Scientist</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, USA USA</t>
+          <t>Celebration, FL, USA USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -894,7 +894,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Gemini, FastAPI, Kubernetes, Terraform, Python, R, Java</t>
+          <t>Data Scientist, RAG, CI/CD, Git, Tableau, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -904,32 +904,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15f8418b1009c354</t>
+          <t>https://www.indeed.com/viewjob?jk=f9d8cb5f3e6c108b</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Consultant - Data Platforms - REMOTE</t>
+          <t>Sr Platform Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Fortified Data</t>
+          <t>The Hershey Company</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Raleigh, NC, USA USA</t>
+          <t>Dallas, TX, USA USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AKS, Snowflake, Databricks, PySpark, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, MLflow, CI/CD, Terraform, Git, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -939,42 +939,217 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73378029918e0cc3</t>
+          <t>https://www.indeed.com/viewjob?jk=86fb867bcabb2d1a</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Pharmacist Data Analyst</t>
+          <t>Senior Software Engineer - Global Dining</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>RedSail Technologies</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, USA USA</t>
+          <t>New York, NY, USA USA</t>
         </is>
       </c>
       <c r="D16" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>CI/CD, Git, Kafka, PostgreSQL, MySQL, MongoDB, SQL, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=66f250709c390530</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>IT Data Analytics Specialist - Data Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Vertiv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Westerville, OH, USA USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Data Scientist, Data Lake, CI/CD, Git, Snowflake, Kafka, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8b1f3467fcbde954</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Engineer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Sunnyvale, CA, USA USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, Kafka, Cassandra, Python, R, Java, C++, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f82ffc6ab6468615</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>AI Machine Learning Engineering Sr</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Lockheed Martin</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, USA USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
         <v>10</v>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Data Scientist, Cortex, CI/CD, Git, Snowflake, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d75daa4f696e2181</t>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, LangChain, RAG, Prompt Engineering, CI/CD, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0184a74f45d13af6</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>AI Machine Learning Engineering Sr</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Lockheed Martin</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Remote, USA USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>10</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, LangChain, Docker, Kubernetes, CI/CD, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=221ba294043b5c5c</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>FLOAT</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>USA USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>10</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Snowflake, BigQuery, Kafka, MongoDB, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5d4b4eda0b8a99d9</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-10-09.xlsx
+++ b/daily_matches/job_matches_2026-10-09.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,25 +456,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr Software Engineer I - Enterprise Architecture</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Florence HC</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, USA USA</t>
+          <t>Atlanta, GA, USA USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>24.4</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
+          <t>Data Scientist, Generative AI, RAG, Copilot, S3, CI/CD, Terraform, Git, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -484,32 +484,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caff522a25e0d7d6</t>
+          <t>https://www.indeed.com/viewjob?jk=5ab1716679382a11</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Gen AI Developer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Dallas, TX, USA USA</t>
+          <t>Dearborn, MI, USA USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Hugging Face, Pinecone, TensorFlow, PyTorch, AWS SageMaker, Azure ML</t>
+          <t>RAG, Copilot, BigQuery, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -519,32 +519,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=966968d140bf48e2</t>
+          <t>https://www.indeed.com/viewjob?jk=719c5a874f118bcf</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Gen AI Developer</t>
+          <t>Data and Analytics Architect - MS Fabric</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>SysLogic, Inc.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Richardson, TX, USA USA</t>
+          <t>Brookfield, WI, USA USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.9</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Hugging Face, Pinecone, TensorFlow, PyTorch, AWS SageMaker, Azure ML</t>
+          <t>RAG, Copilot, Synapse, Data Lake, Dataflow, CI/CD, Git, Snowflake, Databricks, Power BI</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -554,32 +554,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84431b9d5a1a9068</t>
+          <t>https://www.indeed.com/viewjob?jk=105449350f0e9ec0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Financial Services - Forward Deployed Engineer - Technology Consulting - Senior - NYC</t>
+          <t>AI, Data &amp; Automation Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>QualDerm Partners LLC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New York, NY, USA USA</t>
+          <t>Brentwood, TN, USA USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.9</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Copilot, Pinecone, Prompt Engineering, AWS SageMaker, Azure ML, Docker</t>
+          <t>Generative AI, RAG, Prompt Engineering, Cortex, Synapse, CI/CD, Git, Snowflake, Power BI, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -589,32 +589,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83aa91fe9a6b8f53</t>
+          <t>https://www.indeed.com/viewjob?jk=150bee16d3bf5873</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Gen AI Developer</t>
+          <t>Artificial Intelligence/Machine (AI/ML) Learning Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Living Spaces</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Plano, TX, USA USA</t>
+          <t>La Mirada, CA, USA USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.9</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Hugging Face, Pinecone, TensorFlow, PyTorch, AWS SageMaker, Azure ML</t>
+          <t>AI Engineer, RAG, Gemini, TensorFlow, PyTorch, scikit-learn, Azure ML, BigQuery, Databricks, BigQuery</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -624,32 +624,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b98a756d58e2e27</t>
+          <t>https://www.indeed.com/viewjob?jk=4e2391d0042bbe7e</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI Machine Learning Engineering Sr -</t>
+          <t>Sr. Analytics Data Platform Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>DoubleVerify</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>New York, NY, USA USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.8</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, Docker, Kubernetes, Apache Airflow, CI/CD, Git, Kafka</t>
+          <t>RAG, Copilot, BigQuery, Kubernetes, CI/CD, Terraform, Git, Snowflake, BigQuery, Kafka</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -659,32 +659,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25e732a62993b114</t>
+          <t>https://www.indeed.com/viewjob?jk=771ada10ea70766c</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer II</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cleveland Clinic</t>
+          <t>Pursuit Aerospace</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cleveland, OH, USA USA</t>
+          <t>USA USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>Data Scientist, Generative AI, RAG, S3, Data Lake, CI/CD, Git, Snowflake, Python, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -694,32 +694,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c6069a1656fe1c8</t>
+          <t>https://www.indeed.com/viewjob?jk=afd8d15d41de082d</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Full Stack AI Developer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Enterprise Knowledge</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Arlington, VA, USA USA</t>
+          <t>Louisville, KY, USA USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Docker, Git, Python, SQL, R, Java</t>
+          <t>AI Engineer, RAG, Gemini, Docker, Kubernetes, CI/CD, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -729,32 +729,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef4c8960caa195a5</t>
+          <t>https://www.indeed.com/viewjob?jk=7c3adae8783577e5</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer II (Java/Full stack/Cloud)</t>
+          <t>AI - Software Engineering-Sr Professional I</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Westerville, OH, USA USA</t>
+          <t>Alpharetta, GA, USA USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Prompt Engineering, S3, CI/CD, Git, SQL, R, Java</t>
+          <t>RAG, Copilot, Kubernetes, AKS, CI/CD, Git, Snowflake, Kafka, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -764,32 +764,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af75619025565e2d</t>
+          <t>https://www.indeed.com/viewjob?jk=7126fa6216c927d2</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>AI - Software Engineering Advisor I</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Charlotte, NC, USA USA</t>
+          <t>Alpharetta, GA, USA USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Prompt Engineering, S3, Docker, Kubernetes, Git, R, Java</t>
+          <t>RAG, Copilot, Kubernetes, AKS, CI/CD, Git, Snowflake, Kafka, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -799,32 +799,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1db0b10090073bdc</t>
+          <t>https://www.indeed.com/viewjob?jk=b29d0fe789c8060e</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Vibe Coding Engineer</t>
+          <t>Senior Data Scientist (AI-assisted Clinical Development)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Hierarch Soft Technologies Inc,</t>
+          <t>Genentech</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Boston, MA, USA USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, Docker, Kubernetes, Git, Python, R</t>
+          <t>Data Scientist, Generative AI, TensorFlow, PyTorch, scikit-learn, XGBoost, CI/CD, Git, Python, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -834,32 +834,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5745a1b5dcde8af4</t>
+          <t>https://www.indeed.com/viewjob?jk=8bf232b6a8415748</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Cyber -AI Cloud Security Engineer - Consultant</t>
+          <t>AI/ML Engineer - Entry Level</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Calimontex Technologies LLC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>McLean, VA, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Gemini, FastAPI, Kubernetes, Terraform, Python, R, Java</t>
+          <t>Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, scikit-learn, Keras, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -869,32 +869,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2a1f4e5b6141aed</t>
+          <t>https://www.indeed.com/viewjob?jk=8099568c51a63185</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Associate Marketing Data Scientist</t>
+          <t>Senior Full Stack AI Software Engineer (Java)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Celebration, FL, USA USA</t>
+          <t>Irving, TX, USA USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, CI/CD, Git, Tableau, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Copilot, Docker, CI/CD, Git, Kafka, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -904,32 +904,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9d8cb5f3e6c108b</t>
+          <t>https://www.indeed.com/viewjob?jk=9f9cbfb8154d518c</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr Platform Engineer</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>The Hershey Company</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Dallas, TX, USA USA</t>
+          <t>San Francisco, CA, USA USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, MLflow, CI/CD, Terraform, Git, Databricks, Python, SQL, R, Scala</t>
+          <t>Data Scientist, Generative AI, RAG, Docker, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -939,32 +939,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86fb867bcabb2d1a</t>
+          <t>https://www.indeed.com/viewjob?jk=de31b549c0b820bb</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Global Dining</t>
+          <t>Sr. SW Engineer - AI Security</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, USA USA</t>
+          <t>Ashburn, VA, USA USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CI/CD, Git, Kafka, PostgreSQL, MySQL, MongoDB, SQL, R, Java, Optimization</t>
+          <t>Generative AI, LangChain, LLaMA, Docker, Kubernetes, CI/CD, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -974,32 +974,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66f250709c390530</t>
+          <t>https://www.indeed.com/viewjob?jk=e7000f9fc652df76</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>IT Data Analytics Specialist - Data Engineer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Vertiv</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Westerville, OH, USA USA</t>
+          <t>Eden Prairie, MN, USA USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Data Scientist, Data Lake, CI/CD, Git, Snowflake, Kafka, Python, SQL, R, Scala</t>
+          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Terraform, MySQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1009,32 +1009,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b1f3467fcbde954</t>
+          <t>https://www.indeed.com/viewjob?jk=fdaabec313a937df</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer II - Engineer</t>
+          <t>Quant Analytics</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Uber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, USA USA</t>
+          <t>Columbiana, OH, USA USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, Kafka, Cassandra, Python, R, Java, C++, Scala, Optimization</t>
+          <t>Data Scientist, RAG, Data Lake, CI/CD, Git, Databricks, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1044,32 +1044,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f82ffc6ab6468615</t>
+          <t>https://www.indeed.com/viewjob?jk=5223319bf04633de</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AI Machine Learning Engineering Sr</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>Pursuit Aerospace</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, USA USA</t>
+          <t>USA USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, LangChain, RAG, Prompt Engineering, CI/CD, Git, Python, R, Scala</t>
+          <t>Data Scientist, Generative AI, S3, Data Lake, CI/CD, Git, Snowflake, Python, SQL, R</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1079,32 +1079,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0184a74f45d13af6</t>
+          <t>https://www.indeed.com/viewjob?jk=f39d9ceee1fd9624</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AI Machine Learning Engineering Sr</t>
+          <t>Data Masking Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Atlanta, GA, USA USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, LangChain, Docker, Kubernetes, CI/CD, Git, Python, R</t>
+          <t>Generative AI, RAG, Gemini, CI/CD, Jenkins, Git, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1114,42 +1114,602 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=221ba294043b5c5c</t>
+          <t>https://www.indeed.com/viewjob?jk=ba50192afaa67e55</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior QA Automation Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FLOAT</t>
+          <t>Evolent</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
+          <t>Remote, USA USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, FastAPI, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=96dc2ab29920f4ed</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Computational Chemistry &amp; AI/ML Scientist</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>MarLabs</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Remote, USA USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, TensorFlow, PyTorch, scikit-learn, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c17be1a89b635c5c</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Temporal Technologies</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
           <t>USA USA</t>
         </is>
       </c>
-      <c r="D21" t="n">
+      <c r="D23" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Data Scientist, S3, Athena, BigQuery, Snowflake, BigQuery, Python, SQL, R, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8bbc9be55f3c56da</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Infrastructure Engineer - Golang Developer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, USA USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, CI/CD, Git, PostgreSQL, MySQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7efa97b6731af684</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Citi</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>New Castle, DE, USA USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Git, Kafka, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d4c025165e768668</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Cyber -AI Cloud Security Engineer - Consultant</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, USA USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Gemini, FastAPI, Kubernetes, Terraform, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=666703c7985e4d79</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Agentic Software Engineer I</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Austin, TX, USA USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9a8be61409347513</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Senior Applied ML Algorithm Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Whoop</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Boston, MA, USA USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
         <v>10</v>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>RAG, BigQuery, Snowflake, BigQuery, Kafka, MongoDB, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5d4b4eda0b8a99d9</t>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, scikit-learn, Git, Python, R, C++, Optimization</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c9d77f4d72fd4108</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Sr. Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Boulder, CO, USA USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, RAG, Gemini, Kubernetes, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=18a32a04717014e6</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Sr. Data Analyst</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Baylor Scott &amp; White Health</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Remote, USA USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>RAG, Git, Snowflake, Power BI, Python, SQL, R, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=154bae8f5dea18f4</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Data Scientist, Mobile App Performance</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>PubMatic</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Redwood City, CA, USA USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Git, Hadoop, Python, SQL, R, Optimization, Hypothesis Testing</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1a5a6bc22c7d43a5</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer: Retail Media</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Constructor</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Remote, USA USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RAG, Athena, FastAPI, PostgreSQL, MySQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f231dfbb95f9da30</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Clearwater Analytics (CWAN)</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Boise, ID, USA USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, FastAPI, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=248d0df0a6093f24</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Senior Moodle Developer(PHP)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Busoft</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>CA, USA USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>S3, Docker, CI/CD, Git, MySQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d26800dc4ab1e54a</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Specialist Solutions Architect - Azure Infrastructure &amp; AI Platform</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>USA USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>10</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Synapse, Terraform, Snowflake, Databricks, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c5ef033d6bdd0980</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Specialist Solutions Architect - AWS Infrastructure &amp; AI Platform</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>USA USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>10</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Synapse, Terraform, Snowflake, Databricks, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=04eb3364f452214e</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Sr. Automation Engineer - IT Asset Management</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, USA USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>10</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Gemini, Prompt Engineering, Data Lake, Databricks, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aa5a94a41b8da45c</t>
         </is>
       </c>
     </row>
